--- a/artfynd/A 33647-2024 artfynd.xlsx
+++ b/artfynd/A 33647-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536491</v>
+        <v>119537137</v>
       </c>
       <c r="B6" t="n">
-        <v>79517</v>
+        <v>79642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2080</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660967</v>
+        <v>660981</v>
       </c>
       <c r="R6" t="n">
-        <v>7175548</v>
+        <v>7175641</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,12 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>s. lat</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,7 +1217,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1353,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536657</v>
+        <v>119536659</v>
       </c>
       <c r="B8" t="n">
         <v>79607</v>
@@ -1393,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660983</v>
+        <v>660854</v>
       </c>
       <c r="R8" t="n">
-        <v>7175640</v>
+        <v>7175860</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1428,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536661</v>
+        <v>119536663</v>
       </c>
       <c r="B9" t="n">
         <v>79607</v>
@@ -1505,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660949</v>
+        <v>661021</v>
       </c>
       <c r="R9" t="n">
-        <v>7175746</v>
+        <v>7175712</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119537137</v>
+        <v>119536491</v>
       </c>
       <c r="B10" t="n">
-        <v>79642</v>
+        <v>79517</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>2080</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>660981</v>
+        <v>660967</v>
       </c>
       <c r="R10" t="n">
-        <v>7175641</v>
+        <v>7175548</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1652,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1656,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>s. lat</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,6 +1670,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536662</v>
+        <v>119536472</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>84009</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5589</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>660995</v>
+        <v>661051</v>
       </c>
       <c r="R11" t="n">
-        <v>7175736</v>
+        <v>7175710</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536289</v>
+        <v>119536655</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,25 +1813,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>660968</v>
+        <v>660980</v>
       </c>
       <c r="R12" t="n">
-        <v>7175545</v>
+        <v>7175546</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537139</v>
+        <v>119536696</v>
       </c>
       <c r="B13" t="n">
-        <v>79642</v>
+        <v>79643</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,21 +1929,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>660854</v>
+        <v>660968</v>
       </c>
       <c r="R13" t="n">
-        <v>7175860</v>
+        <v>7175545</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,7 +2025,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536658</v>
+        <v>119536660</v>
       </c>
       <c r="B14" t="n">
         <v>79607</v>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>660932</v>
+        <v>660883</v>
       </c>
       <c r="R14" t="n">
-        <v>7175658</v>
+        <v>7175819</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,7 +2137,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536660</v>
+        <v>119536658</v>
       </c>
       <c r="B15" t="n">
         <v>79607</v>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>660883</v>
+        <v>660932</v>
       </c>
       <c r="R15" t="n">
-        <v>7175819</v>
+        <v>7175658</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536696</v>
+        <v>119536743</v>
       </c>
       <c r="B16" t="n">
-        <v>79643</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,25 +2261,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>660968</v>
+        <v>661007</v>
       </c>
       <c r="R16" t="n">
-        <v>7175545</v>
+        <v>7175727</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,7 +2361,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536656</v>
+        <v>119536661</v>
       </c>
       <c r="B17" t="n">
         <v>79607</v>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>660968</v>
+        <v>660949</v>
       </c>
       <c r="R17" t="n">
-        <v>7175545</v>
+        <v>7175746</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2473,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536472</v>
+        <v>119537139</v>
       </c>
       <c r="B18" t="n">
-        <v>84009</v>
+        <v>79642</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,25 +2485,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5589</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>661051</v>
+        <v>660854</v>
       </c>
       <c r="R18" t="n">
-        <v>7175710</v>
+        <v>7175860</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2585,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119537024</v>
+        <v>119537138</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2597,20 +2597,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>660894</v>
+        <v>660930</v>
       </c>
       <c r="R19" t="n">
-        <v>7175789</v>
+        <v>7175662</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2697,7 +2697,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536655</v>
+        <v>119536657</v>
       </c>
       <c r="B20" t="n">
         <v>79607</v>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>660980</v>
+        <v>660983</v>
       </c>
       <c r="R20" t="n">
-        <v>7175546</v>
+        <v>7175640</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,10 +2809,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536743</v>
+        <v>119537024</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2821,25 +2821,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>661007</v>
+        <v>660894</v>
       </c>
       <c r="R21" t="n">
-        <v>7175727</v>
+        <v>7175789</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2921,10 +2921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536408</v>
+        <v>119536656</v>
       </c>
       <c r="B22" t="n">
-        <v>79511</v>
+        <v>79607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2933,25 +2933,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660996</v>
+        <v>660968</v>
       </c>
       <c r="R22" t="n">
-        <v>7175740</v>
+        <v>7175545</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119537138</v>
+        <v>119536408</v>
       </c>
       <c r="B23" t="n">
-        <v>79642</v>
+        <v>79511</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660930</v>
+        <v>660996</v>
       </c>
       <c r="R23" t="n">
-        <v>7175662</v>
+        <v>7175740</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536659</v>
+        <v>119536289</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3157,25 +3157,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>660854</v>
+        <v>660968</v>
       </c>
       <c r="R24" t="n">
-        <v>7175860</v>
+        <v>7175545</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,7 +3257,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536663</v>
+        <v>119536662</v>
       </c>
       <c r="B25" t="n">
         <v>79607</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>661021</v>
+        <v>660995</v>
       </c>
       <c r="R25" t="n">
-        <v>7175712</v>
+        <v>7175736</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 33647-2024 artfynd.xlsx
+++ b/artfynd/A 33647-2024 artfynd.xlsx
@@ -2025,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536660</v>
+        <v>119536743</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,25 +2037,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>660883</v>
+        <v>661007</v>
       </c>
       <c r="R14" t="n">
-        <v>7175819</v>
+        <v>7175727</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536743</v>
+        <v>119536660</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,25 +2261,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661007</v>
+        <v>660883</v>
       </c>
       <c r="R16" t="n">
-        <v>7175727</v>
+        <v>7175819</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 33647-2024 artfynd.xlsx
+++ b/artfynd/A 33647-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119537137</v>
+        <v>119536655</v>
       </c>
       <c r="B6" t="n">
-        <v>79642</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660981</v>
+        <v>660980</v>
       </c>
       <c r="R6" t="n">
-        <v>7175641</v>
+        <v>7175546</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536695</v>
+        <v>119536472</v>
       </c>
       <c r="B7" t="n">
-        <v>79643</v>
+        <v>84009</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>5589</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>660981</v>
+        <v>661051</v>
       </c>
       <c r="R7" t="n">
-        <v>7175540</v>
+        <v>7175710</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536659</v>
+        <v>119537139</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>79642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536491</v>
+        <v>119536743</v>
       </c>
       <c r="B10" t="n">
-        <v>79517</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2080</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>660967</v>
+        <v>661007</v>
       </c>
       <c r="R10" t="n">
-        <v>7175548</v>
+        <v>7175727</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,12 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>s. lat</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,7 +1665,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1689,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536472</v>
+        <v>119536491</v>
       </c>
       <c r="B11" t="n">
-        <v>84009</v>
+        <v>79517</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5589</v>
+        <v>2080</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661051</v>
+        <v>660967</v>
       </c>
       <c r="R11" t="n">
-        <v>7175710</v>
+        <v>7175548</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1764,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1768,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>s. lat</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,6 +1782,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536655</v>
+        <v>119536658</v>
       </c>
       <c r="B12" t="n">
         <v>79607</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>660980</v>
+        <v>660932</v>
       </c>
       <c r="R12" t="n">
-        <v>7175546</v>
+        <v>7175658</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536696</v>
+        <v>119537137</v>
       </c>
       <c r="B13" t="n">
-        <v>79643</v>
+        <v>79642</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,21 +1929,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>660968</v>
+        <v>660981</v>
       </c>
       <c r="R13" t="n">
-        <v>7175545</v>
+        <v>7175641</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536743</v>
+        <v>119536661</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,25 +2037,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661007</v>
+        <v>660949</v>
       </c>
       <c r="R14" t="n">
-        <v>7175727</v>
+        <v>7175746</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536658</v>
+        <v>119536695</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,25 +2149,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>660932</v>
+        <v>660981</v>
       </c>
       <c r="R15" t="n">
-        <v>7175658</v>
+        <v>7175540</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,7 +2249,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536660</v>
+        <v>119536662</v>
       </c>
       <c r="B16" t="n">
         <v>79607</v>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>660883</v>
+        <v>660995</v>
       </c>
       <c r="R16" t="n">
-        <v>7175819</v>
+        <v>7175736</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,7 +2361,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536661</v>
+        <v>119536660</v>
       </c>
       <c r="B17" t="n">
         <v>79607</v>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>660949</v>
+        <v>660883</v>
       </c>
       <c r="R17" t="n">
-        <v>7175746</v>
+        <v>7175819</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2473,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119537139</v>
+        <v>119536408</v>
       </c>
       <c r="B18" t="n">
-        <v>79642</v>
+        <v>79511</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,21 +2489,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>660854</v>
+        <v>660996</v>
       </c>
       <c r="R18" t="n">
-        <v>7175860</v>
+        <v>7175740</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2585,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119537138</v>
+        <v>119537024</v>
       </c>
       <c r="B19" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2597,20 +2597,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>660930</v>
+        <v>660894</v>
       </c>
       <c r="R19" t="n">
-        <v>7175662</v>
+        <v>7175789</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2697,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536657</v>
+        <v>119536289</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,25 +2709,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>660983</v>
+        <v>660968</v>
       </c>
       <c r="R20" t="n">
-        <v>7175640</v>
+        <v>7175545</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,10 +2809,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119537024</v>
+        <v>119536657</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>660894</v>
+        <v>660983</v>
       </c>
       <c r="R21" t="n">
-        <v>7175789</v>
+        <v>7175640</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536408</v>
+        <v>119536659</v>
       </c>
       <c r="B23" t="n">
-        <v>79511</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3045,25 +3045,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660996</v>
+        <v>660854</v>
       </c>
       <c r="R23" t="n">
-        <v>7175740</v>
+        <v>7175860</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536289</v>
+        <v>119536696</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>79643</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536662</v>
+        <v>119537138</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>79642</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,25 +3269,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>660995</v>
+        <v>660930</v>
       </c>
       <c r="R25" t="n">
-        <v>7175736</v>
+        <v>7175662</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
